--- a/data/trans_orig/Q61A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de meses que lleva en paro</t>
+          <t>Número medio de meses que lleva en paro (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,54</t>
+          <t>2,72; 6,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 19,77</t>
+          <t>12,54; 19,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 30,61</t>
+          <t>18,74; 30,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 27,15</t>
+          <t>9,92; 26,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,31</t>
+          <t>2,08; 4,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 22,49</t>
+          <t>9,27; 21,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 21,68</t>
+          <t>10,04; 21,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 33,82</t>
+          <t>16,33; 33,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,12</t>
+          <t>2,87; 5,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 18,68</t>
+          <t>12,57; 18,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 24,98</t>
+          <t>16,03; 24,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 28,37</t>
+          <t>15,67; 27,25</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,93</t>
+          <t>4,53; 9,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 20,26</t>
+          <t>13,12; 19,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,55</t>
+          <t>13,48; 18,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 30,2</t>
+          <t>12,97; 28,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 16,71</t>
+          <t>5,1; 16,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 22,41</t>
+          <t>13,28; 22,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,63; 29,79</t>
+          <t>18,59; 28,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,34; 39,49</t>
+          <t>21,48; 40,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,18</t>
+          <t>5,3; 10,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 19,2</t>
+          <t>14,09; 18,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 22,09</t>
+          <t>16,54; 21,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 30,54</t>
+          <t>18,81; 30,99</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,25</t>
+          <t>3,17; 8,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 34,33</t>
+          <t>13,7; 35,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 26,59</t>
+          <t>13,21; 26,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 36,95</t>
+          <t>16,83; 36,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 25,73</t>
+          <t>5,37; 24,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 22,01</t>
+          <t>12,83; 21,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,43; 30,0</t>
+          <t>19,3; 29,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 32,33</t>
+          <t>13,33; 29,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 14,38</t>
+          <t>4,88; 13,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,39; 25,8</t>
+          <t>14,47; 27,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,55; 26,44</t>
+          <t>18,3; 26,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,93; 27,98</t>
+          <t>16,34; 28,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 45,33</t>
+          <t>3,42; 44,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 24,47</t>
+          <t>13,74; 25,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,76; 35,69</t>
+          <t>24,0; 35,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 25,92</t>
+          <t>12,35; 26,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,4</t>
+          <t>3,84; 7,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,21; 25,47</t>
+          <t>14,99; 26,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 39,32</t>
+          <t>23,6; 38,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 39,95</t>
+          <t>13,47; 42,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 24,73</t>
+          <t>4,35; 24,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,24; 22,24</t>
+          <t>15,36; 22,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 34,7</t>
+          <t>24,95; 34,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,89; 32,94</t>
+          <t>15,09; 31,38</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,84</t>
+          <t>2,24; 6,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 17,58</t>
+          <t>11,23; 17,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 24,52</t>
+          <t>14,37; 24,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 48,96</t>
+          <t>9,43; 47,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,1</t>
+          <t>3,23; 8,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 19,65</t>
+          <t>10,18; 20,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,65; 27,35</t>
+          <t>17,85; 27,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 21,72</t>
+          <t>5,65; 22,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,82</t>
+          <t>3,24; 6,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,13</t>
+          <t>11,83; 17,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,65; 24,22</t>
+          <t>17,66; 24,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 38,54</t>
+          <t>10,31; 37,71</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,39</t>
+          <t>3,36; 10,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,73</t>
+          <t>6,6; 10,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 17,61</t>
+          <t>9,81; 17,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 25,91</t>
+          <t>9,96; 25,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,91; 43,48</t>
+          <t>5,23; 56,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 19,55</t>
+          <t>9,06; 19,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 16,95</t>
+          <t>7,82; 15,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,92; 21,38</t>
+          <t>10,73; 20,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,14; 25,34</t>
+          <t>4,97; 28,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 14,27</t>
+          <t>8,68; 14,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,43; 15,38</t>
+          <t>9,96; 15,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,31; 20,78</t>
+          <t>11,37; 20,18</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,3</t>
+          <t>3,79; 8,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,1; 16,35</t>
+          <t>11,98; 16,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,26</t>
+          <t>11,44; 19,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,69; 53,52</t>
+          <t>20,86; 50,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,42</t>
+          <t>4,67; 8,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 35,01</t>
+          <t>16,43; 33,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 29,67</t>
+          <t>14,76; 28,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,89; 47,43</t>
+          <t>26,03; 49,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,6</t>
+          <t>4,67; 7,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,18</t>
+          <t>14,54; 22,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,0; 21,2</t>
+          <t>13,99; 22,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,81; 44,52</t>
+          <t>25,95; 43,7</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,3</t>
+          <t>4,8; 9,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,46; 17,39</t>
+          <t>11,58; 17,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,37; 22,7</t>
+          <t>16,2; 22,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,56; 20,29</t>
+          <t>12,54; 20,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,51</t>
+          <t>5,89; 9,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,59</t>
+          <t>16,72; 25,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,52; 31,85</t>
+          <t>20,38; 31,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,48; 17,98</t>
+          <t>13,43; 18,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,0</t>
+          <t>6,09; 9,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,72; 20,0</t>
+          <t>14,64; 19,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 25,9</t>
+          <t>19,18; 25,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,68; 17,87</t>
+          <t>13,91; 18,05</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,89</t>
+          <t>5,08; 8,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,59</t>
+          <t>13,74; 16,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,12; 21,33</t>
+          <t>18,23; 21,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,54; 25,22</t>
+          <t>17,51; 25,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,57</t>
+          <t>6,21; 10,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,38; 20,92</t>
+          <t>16,35; 21,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,54; 25,21</t>
+          <t>20,8; 25,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,5; 27,04</t>
+          <t>20,39; 26,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,68</t>
+          <t>5,93; 8,74</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15,28; 17,63</t>
+          <t>15,25; 17,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,59</t>
+          <t>19,8; 22,52</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,68</t>
+          <t>19,81; 24,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q61A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,56</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,73</t>
+          <t>21,72</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>18,93</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,5</t>
+          <t>2,72; 6,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 19,8</t>
+          <t>12,85; 19,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 30,65</t>
+          <t>18,61; 30,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 26,96</t>
+          <t>8,58; 23,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,42</t>
+          <t>2,09; 4,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 21,32</t>
+          <t>9,19; 21,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,04; 21,48</t>
+          <t>9,71; 23,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 33,35</t>
+          <t>16,05; 30,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,11</t>
+          <t>2,83; 5,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,96</t>
+          <t>12,56; 18,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 24,2</t>
+          <t>15,93; 24,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,67; 27,25</t>
+          <t>14,64; 25,32</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,19</t>
+          <t>19,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,19</t>
+          <t>28,46</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,85</t>
+          <t>24,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,93</t>
+          <t>4,55; 9,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,79</t>
+          <t>13,28; 19,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 18,7</t>
+          <t>13,45; 18,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 28,51</t>
+          <t>13,11; 27,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 16,86</t>
+          <t>5,09; 16,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,28; 22,7</t>
+          <t>13,88; 22,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,59; 28,95</t>
+          <t>18,62; 29,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,48; 40,4</t>
+          <t>21,72; 39,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,21</t>
+          <t>5,24; 10,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,83</t>
+          <t>14,24; 19,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 21,87</t>
+          <t>16,35; 21,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 30,99</t>
+          <t>19,0; 30,57</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,77</t>
+          <t>23,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,31</t>
+          <t>17,94</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>19,97</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,52</t>
+          <t>3,33; 8,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 35,47</t>
+          <t>13,46; 39,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 26,65</t>
+          <t>13,05; 26,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 36,91</t>
+          <t>15,99; 34,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 24,58</t>
+          <t>5,18; 23,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,83; 21,45</t>
+          <t>13,18; 21,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 29,85</t>
+          <t>19,62; 29,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 29,65</t>
+          <t>13,48; 32,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 13,96</t>
+          <t>5,0; 14,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 27,25</t>
+          <t>14,13; 27,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,4</t>
+          <t>18,09; 26,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,34; 28,31</t>
+          <t>15,38; 27,08</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,69</t>
+          <t>24,35</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,88</t>
+          <t>25,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,07</t>
+          <t>25,28</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 44,06</t>
+          <t>3,38; 46,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 25,13</t>
+          <t>13,63; 24,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,0; 35,5</t>
+          <t>24,18; 35,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 26,53</t>
+          <t>16,12; 42,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,51</t>
+          <t>3,91; 7,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 26,36</t>
+          <t>15,12; 25,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,6; 38,52</t>
+          <t>22,93; 37,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 42,13</t>
+          <t>15,21; 48,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 24,89</t>
+          <t>4,46; 26,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 22,84</t>
+          <t>15,24; 22,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 34,45</t>
+          <t>25,14; 34,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 31,38</t>
+          <t>16,5; 37,0</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,53</t>
+          <t>21,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>11,42</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,95</t>
+          <t>18,09</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,82</t>
+          <t>2,36; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 17,43</t>
+          <t>11,35; 17,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 24,41</t>
+          <t>14,65; 25,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,43; 47,65</t>
+          <t>8,46; 45,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,39</t>
+          <t>3,26; 8,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 20,31</t>
+          <t>9,83; 19,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 27,3</t>
+          <t>17,5; 26,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 22,97</t>
+          <t>4,64; 19,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,65</t>
+          <t>3,38; 6,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,32</t>
+          <t>11,57; 17,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 24,7</t>
+          <t>17,51; 24,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 37,71</t>
+          <t>9,66; 37,68</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,49</t>
+          <t>14,05</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,92</t>
+          <t>14,28</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 10,69</t>
+          <t>3,47; 10,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 10,81</t>
+          <t>6,6; 10,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,37</t>
+          <t>9,81; 17,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 25,94</t>
+          <t>8,71; 22,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 56,56</t>
+          <t>4,96; 42,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 19,13</t>
+          <t>9,42; 20,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 15,96</t>
+          <t>7,49; 16,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 20,89</t>
+          <t>10,94; 19,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 28,03</t>
+          <t>5,05; 28,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,68; 14,73</t>
+          <t>8,77; 14,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 15,88</t>
+          <t>9,79; 15,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,37; 20,18</t>
+          <t>10,91; 18,97</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,29</t>
+          <t>30,04</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>34,88</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,13</t>
+          <t>32,83</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,11</t>
+          <t>3,88; 8,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,23</t>
+          <t>12,1; 16,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 19,16</t>
+          <t>11,43; 19,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,86; 50,04</t>
+          <t>19,52; 50,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,26</t>
+          <t>4,72; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,43; 33,58</t>
+          <t>16,91; 33,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,76; 28,41</t>
+          <t>14,52; 28,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,03; 49,77</t>
+          <t>26,97; 47,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,87</t>
+          <t>4,5; 7,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,54; 22,28</t>
+          <t>14,68; 22,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,28</t>
+          <t>13,7; 21,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,95; 43,7</t>
+          <t>24,83; 42,67</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,12</t>
+          <t>16,17</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15,62</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,83</t>
+          <t>15,92</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,24</t>
+          <t>4,88; 9,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,58; 17,17</t>
+          <t>11,5; 17,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,44</t>
+          <t>16,35; 22,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,14</t>
+          <t>12,82; 20,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,56</t>
+          <t>5,9; 9,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,72; 25,44</t>
+          <t>16,57; 25,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,38; 31,83</t>
+          <t>20,26; 32,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,43; 18,03</t>
+          <t>13,61; 18,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,12</t>
+          <t>6,02; 8,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,64; 19,84</t>
+          <t>14,73; 20,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,18; 25,48</t>
+          <t>19,13; 25,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,91; 18,05</t>
+          <t>14,0; 17,93</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20,87</t>
+          <t>20,29</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23,15</t>
+          <t>23,36</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,15</t>
+          <t>22,02</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,78</t>
+          <t>5,02; 8,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,52</t>
+          <t>13,76; 16,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,43</t>
+          <t>18,09; 21,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,29</t>
+          <t>17,37; 24,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,69</t>
+          <t>6,23; 11,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,01</t>
+          <t>16,42; 20,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,22</t>
+          <t>20,77; 25,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,96</t>
+          <t>20,59; 26,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,74</t>
+          <t>5,91; 8,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15,25; 17,63</t>
+          <t>15,23; 17,64</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,52</t>
+          <t>19,72; 22,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,81; 24,9</t>
+          <t>19,66; 24,45</t>
         </is>
       </c>
     </row>
